--- a/lead_generation_forms/032_seasonal_landscaping_services_lead_generation_form--lead_generation_forms.xlsx
+++ b/lead_generation_forms/032_seasonal_landscaping_services_lead_generation_form--lead_generation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'first_name',_'label':_'first_name'}</t>
+          <t>first_name</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'First Name', 'label': 'First Name'}</t>
+          <t>First Name</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'last_name',_'label':_'last_name'}</t>
+          <t>last_name</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'Last Name', 'label': 'Last Name'}</t>
+          <t>Last Name</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'email',_'label':_'email'}</t>
+          <t>email</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'Email', 'label': 'Email'}</t>
+          <t>Email</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'phone',_'label':_'phone'}</t>
+          <t>phone</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'Phone', 'label': 'Phone'}</t>
+          <t>Phone</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'lawn_maintenance',_'label':_'lawn_maintenance'}</t>
+          <t>lawn_maintenance</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'Lawn Maintenance', 'label': 'Lawn Maintenance'}</t>
+          <t>Lawn Maintenance</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'yard_work',_'label':_'yard_work'}</t>
+          <t>yard_work</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'Yard Work', 'label': 'Yard Work'}</t>
+          <t>Yard Work</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'tree_trimming',_'label':_'tree_trimming'}</t>
+          <t>tree_trimming</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'Tree Trimming', 'label': 'Tree Trimming'}</t>
+          <t>Tree Trimming</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'garden_design',_'label':_'garden_design'}</t>
+          <t>garden_design</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'Garden Design', 'label': 'Garden Design'}</t>
+          <t>Garden Design</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'residential',_'label':_'residential'}</t>
+          <t>residential</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'Residential', 'label': 'Residential'}</t>
+          <t>Residential</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'commercial',_'label':_'commercial'}</t>
+          <t>commercial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'Commercial', 'label': 'Commercial'}</t>
+          <t>Commercial</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'other',_'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'Other', 'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'submit',_'label':_'submit'}</t>
+          <t>submit</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'Submit', 'label': 'Submit'}</t>
+          <t>Submit</t>
         </is>
       </c>
     </row>
